--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-25.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F651"/>
+  <dimension ref="A1:F695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -930,12 +930,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -952,12 +952,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1398,22 +1398,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1424,26 +1428,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1686,26 +1686,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>8.098M</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>7.70M</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -1716,26 +1712,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1746,22 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1776,15 +1772,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1802,22 +1802,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1832,22 +1832,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1862,18 +1862,18 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -2860,26 +2860,26 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -2890,26 +2890,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>256K</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2920,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2950,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2980,22 +2976,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3006,26 +3002,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3036,26 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3066,22 +3062,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>256K</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3092,18 +3092,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3118,22 +3122,18 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3282,14 +3282,10 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>12.074B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
@@ -3304,12 +3300,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3326,12 +3322,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3348,10 +3344,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - CornDEC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>12.074B</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3532,26 +3532,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -3562,26 +3558,26 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
@@ -3592,22 +3588,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3622,22 +3618,18 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3652,18 +3644,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3678,18 +3674,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,12 +3704,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3719,11 +3719,11 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -3922,18 +3922,18 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3966,18 +3966,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4010,26 +4010,26 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4070,26 +4070,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4100,22 +4100,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4130,22 +4130,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4160,22 +4160,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4556,24 +4556,16 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="n">
         <v>3</v>
       </c>
@@ -4586,18 +4578,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -4608,26 +4608,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -4638,26 +4638,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4668,22 +4668,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4694,22 +4698,26 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -4720,18 +4728,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -4742,16 +4758,20 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4764,12 +4784,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -4786,20 +4806,16 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4812,26 +4828,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -4842,26 +4850,22 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
@@ -4872,26 +4876,22 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4902,26 +4902,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4932,26 +4932,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4962,26 +4962,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4992,16 +4984,24 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5014,26 +5014,26 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
@@ -5044,22 +5044,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5074,17 +5074,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190">
@@ -5240,26 +5240,22 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
@@ -5270,26 +5266,22 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Building Permits PrelDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1.48M</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
@@ -5300,22 +5292,26 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
+          <t>1.499M</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>1.32M</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -5326,22 +5322,26 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Building Permits PrelDEC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>1.48M</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -5538,18 +5538,22 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentNOV</t>
+          <t>Net Long-term TIC FlowsNOV</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>$-15.8B</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr"/>
+          <t>$79B</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>$159.9B</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208">
@@ -5560,22 +5564,18 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsNOV</t>
+          <t>Overall Net Capital FlowsNOV</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>$79B</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
           <t>$159.9B</t>
         </is>
       </c>
+      <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="209">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsNOV</t>
+          <t>Foreign Bond InvestmentNOV</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>$159.9B</t>
+          <t>$-15.8B</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Purchase IndexJAN/17</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -5736,18 +5736,18 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217">
@@ -5758,18 +5758,18 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="218">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -5802,12 +5802,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -6150,12 +6150,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6172,12 +6172,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6194,22 +6194,18 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -6220,18 +6216,22 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -6242,19 +6242,15 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
         <v>3</v>
@@ -6268,12 +6264,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6290,22 +6286,18 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
@@ -6316,18 +6308,22 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -6338,12 +6334,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6360,12 +6356,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,15 +6378,19 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.043M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
         <v>3</v>
@@ -6534,26 +6534,26 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="250">
@@ -6564,26 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6594,22 +6594,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -6620,26 +6624,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
@@ -6650,26 +6650,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
@@ -6710,22 +6710,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F255" t="n">
@@ -6870,18 +6870,22 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>New Home Sales MoMDEC</t>
+          <t>New Home SalesDEC</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr"/>
+          <t>0.698M</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>0.67M</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>0.64M</t>
         </is>
       </c>
       <c r="F261" t="n">
@@ -6896,22 +6900,18 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>New Home SalesDEC</t>
+          <t>New Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>0.698M</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>0.67M</t>
-        </is>
-      </c>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
-          <t>0.64M</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2-Year Note Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>4.211%</t>
+          <t>4.140%</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>2-Year Note Auction</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>4.140%</t>
+          <t>4.211%</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -7178,18 +7178,18 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -7204,22 +7204,26 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
@@ -7260,26 +7264,22 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
@@ -7290,18 +7290,18 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Money SupplyDEC</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>$21.53T</t>
+          <t>4.457%</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Money SupplyDEC</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>4.457%</t>
+          <t>$21.53T</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -7790,18 +7790,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298">
@@ -7812,12 +7816,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7834,22 +7838,22 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -7860,12 +7864,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7882,12 +7886,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7904,12 +7908,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7926,22 +7930,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>3.2M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -7952,12 +7956,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7974,22 +7978,18 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -8324,18 +8324,22 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8350,22 +8354,18 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8516,22 +8516,18 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F326" t="n">
@@ -8546,26 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -8576,26 +8572,26 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
@@ -8606,26 +8602,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -8636,12 +8632,20 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr"/>
+          <t>Employment Cost - Benefits QoQQ4</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
       <c r="D330" t="inlineStr"/>
-      <c r="E330" t="inlineStr"/>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F330" t="n">
         <v>2</v>
       </c>
@@ -8654,22 +8658,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="332">
@@ -8680,7 +8688,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -8688,7 +8696,11 @@
           <t>0.9%</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8706,26 +8718,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -8736,26 +8748,26 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -8766,26 +8778,14 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr"/>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="inlineStr"/>
       <c r="F335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,18 +9472,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -9516,18 +9516,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9768,22 +9768,26 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F376" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="377">
@@ -9794,18 +9798,18 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F377" t="n">
@@ -9820,18 +9824,18 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F378" t="n">
@@ -9846,18 +9850,18 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F379" t="n">
@@ -9872,26 +9876,22 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F380" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="381">
@@ -9902,22 +9902,18 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="382">
@@ -9928,12 +9924,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9950,12 +9946,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,18 +9968,22 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
@@ -9994,22 +9994,22 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2.233M</t>
+          <t>-5.471M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>1.2M</t>
+          <t>-1.5M</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="386">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10064,18 +10064,22 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
@@ -10086,19 +10090,15 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
         <v>3</v>
@@ -10196,22 +10196,22 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F394" t="n">
@@ -10226,26 +10226,26 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="396">
@@ -10256,26 +10256,26 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="397">
@@ -10286,22 +10286,26 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>216.75K</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr"/>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>1.4%</t>
+        </is>
+      </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F397" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="398">
@@ -10312,26 +10316,22 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>219K</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>216.75K</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr"/>
       <c r="E398" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="399">
@@ -10536,22 +10536,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
@@ -10562,26 +10562,26 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
           <t>4.1%</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
@@ -10592,22 +10592,26 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -10618,26 +10622,26 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="412">
@@ -10648,22 +10652,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10678,22 +10682,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10708,26 +10712,26 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415">
@@ -10738,26 +10742,22 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10768,26 +10768,26 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
@@ -10798,22 +10798,22 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
@@ -10904,26 +10904,26 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="423">
@@ -10934,18 +10934,18 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D423" t="inlineStr"/>
       <c r="E423" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10960,22 +10960,22 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F424" t="n">
@@ -10990,22 +10990,22 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11020,18 +11020,18 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -11046,26 +11046,26 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F427" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="428">
@@ -11474,14 +11474,14 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr"/>
       <c r="F447" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="448">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
@@ -11510,14 +11510,14 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr"/>
       <c r="F449" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="450">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -11546,7 +11546,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,14 +11734,14 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr"/>
       <c r="F459" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
@@ -11752,14 +11752,14 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="461">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -11788,7 +11788,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11824,14 +11824,14 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="465">
@@ -11842,14 +11842,14 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
       <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr"/>
       <c r="F465" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="466">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -12360,22 +12360,18 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F490" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="491">
@@ -12386,18 +12382,18 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
       <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F491" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="492">
@@ -12408,7 +12404,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
@@ -12434,22 +12430,18 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F493" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="494">
@@ -12460,14 +12452,14 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F494" t="n">
@@ -12482,7 +12474,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
@@ -12508,18 +12500,18 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F496" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="497">
@@ -12530,18 +12522,22 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
-      <c r="D497" t="inlineStr"/>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F497" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="498">
@@ -12552,18 +12548,22 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
-      <c r="D498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F498" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="499">
@@ -12833,12 +12833,12 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>2025-02-17 18:00:00-05:00</t>
+          <t>2025-02-17 10:20:00-05:00</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C511" t="inlineStr"/>
@@ -12851,25 +12851,17 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>2025-02-18 08:30:00-05:00</t>
+          <t>2025-02-17 18:00:00-05:00</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexFEB</t>
+          <t>Fed Waller Speech</t>
         </is>
       </c>
       <c r="C512" t="inlineStr"/>
-      <c r="D512" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="E512" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="D512" t="inlineStr"/>
+      <c r="E512" t="inlineStr"/>
       <c r="F512" t="n">
         <v>2</v>
       </c>
@@ -12877,12 +12869,12 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>2025-02-18 08:30:00-05:00</t>
+          <t>2025-02-17 18:00:00-05:00</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexFEB</t>
+          <t>Fed Waller Speech</t>
         </is>
       </c>
       <c r="C513" t="inlineStr"/>
@@ -12895,17 +12887,25 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>2025-02-18 10:00:00-05:00</t>
+          <t>2025-02-18 08:30:00-05:00</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexFEB</t>
+          <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C514" t="inlineStr"/>
-      <c r="D514" t="inlineStr"/>
-      <c r="E514" t="inlineStr"/>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="F514" t="n">
         <v>2</v>
       </c>
@@ -12913,25 +12913,17 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>2025-02-18 10:00:00-05:00</t>
+          <t>2025-02-18 08:30:00-05:00</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexFEB</t>
+          <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C515" t="inlineStr"/>
-      <c r="D515" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="E515" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+      <c r="D515" t="inlineStr"/>
+      <c r="E515" t="inlineStr"/>
       <c r="F515" t="n">
         <v>2</v>
       </c>
@@ -12939,17 +12931,25 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>2025-02-18 10:20:00-05:00</t>
+          <t>2025-02-18 10:00:00-05:00</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>NAHB Housing Market IndexFEB</t>
         </is>
       </c>
       <c r="C516" t="inlineStr"/>
-      <c r="D516" t="inlineStr"/>
-      <c r="E516" t="inlineStr"/>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
       <c r="F516" t="n">
         <v>2</v>
       </c>
@@ -12957,55 +12957,63 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>2025-02-18 11:30:00-05:00</t>
+          <t>2025-02-18 10:00:00-05:00</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>NAHB Housing Market IndexFEB</t>
         </is>
       </c>
       <c r="C517" t="inlineStr"/>
-      <c r="D517" t="inlineStr"/>
-      <c r="E517" t="inlineStr"/>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
       <c r="F517" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>2025-02-18 11:30:00-05:00</t>
+          <t>2025-02-18 10:20:00-05:00</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C518" t="inlineStr"/>
       <c r="D518" t="inlineStr"/>
       <c r="E518" t="inlineStr"/>
       <c r="F518" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>2025-02-18 11:30:00-05:00</t>
+          <t>2025-02-18 10:20:00-05:00</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C519" t="inlineStr"/>
       <c r="D519" t="inlineStr"/>
       <c r="E519" t="inlineStr"/>
       <c r="F519" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="520">
@@ -13029,12 +13037,12 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>2025-02-18 12:00:00-05:00</t>
+          <t>2025-02-18 11:30:00-05:00</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>NOPA Crush Report</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
@@ -13047,12 +13055,12 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>2025-02-18 12:00:00-05:00</t>
+          <t>2025-02-18 11:30:00-05:00</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>NOPA Crush Report</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C522" t="inlineStr"/>
@@ -13065,30 +13073,30 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>2025-02-18 13:00:00-05:00</t>
+          <t>2025-02-18 11:30:00-05:00</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
       <c r="D523" t="inlineStr"/>
       <c r="E523" t="inlineStr"/>
       <c r="F523" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>2025-02-18 13:00:00-05:00</t>
+          <t>2025-02-18 11:30:00-05:00</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C524" t="inlineStr"/>
@@ -13101,12 +13109,12 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>2025-02-18 16:00:00-05:00</t>
+          <t>2025-02-18 12:00:00-05:00</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>NOPA Crush Report</t>
         </is>
       </c>
       <c r="C525" t="inlineStr"/>
@@ -13119,12 +13127,12 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>2025-02-18 16:00:00-05:00</t>
+          <t>2025-02-18 12:00:00-05:00</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>NOPA Crush Report</t>
         </is>
       </c>
       <c r="C526" t="inlineStr"/>
@@ -13137,30 +13145,30 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>2025-02-18 16:00:00-05:00</t>
+          <t>2025-02-18 13:00:00-05:00</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr"/>
       <c r="F527" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>2025-02-18 16:00:00-05:00</t>
+          <t>2025-02-18 13:00:00-05:00</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C528" t="inlineStr"/>
@@ -13173,12 +13181,12 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>2025-02-18 16:00:00-05:00</t>
+          <t>2025-02-18 13:00:00-05:00</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
@@ -13191,52 +13199,52 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>2025-02-18 16:00:00-05:00</t>
+          <t>2025-02-18 13:00:00-05:00</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
-      <c r="D530" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr"/>
       <c r="F530" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>2025-02-19 07:00:00-05:00</t>
+          <t>2025-02-18 16:00:00-05:00</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
-      <c r="D531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E531" t="inlineStr"/>
       <c r="F531" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>2025-02-19 07:00:00-05:00</t>
+          <t>2025-02-18 16:00:00-05:00</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
@@ -13249,30 +13257,34 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>2025-02-19 07:00:00-05:00</t>
+          <t>2025-02-18 16:00:00-05:00</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
-      <c r="D533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E533" t="inlineStr"/>
       <c r="F533" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>2025-02-19 07:00:00-05:00</t>
+          <t>2025-02-18 16:00:00-05:00</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
@@ -13285,37 +13297,37 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>2025-02-19 07:00:00-05:00</t>
+          <t>2025-02-18 16:00:00-05:00</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
       <c r="D535" t="inlineStr"/>
       <c r="E535" t="inlineStr"/>
       <c r="F535" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>2025-02-19 07:00:00-05:00</t>
+          <t>2025-02-18 16:00:00-05:00</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="537">
@@ -13326,14 +13338,14 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
       <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr"/>
       <c r="F537" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="538">
@@ -13344,7 +13356,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
@@ -13380,7 +13392,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13393,52 +13405,48 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>2025-02-19 08:30:00-05:00</t>
+          <t>2025-02-19 07:00:00-05:00</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr"/>
-      <c r="E541" t="inlineStr">
-        <is>
-          <t>-9.0%</t>
-        </is>
-      </c>
+      <c r="E541" t="inlineStr"/>
       <c r="F541" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>2025-02-19 08:30:00-05:00</t>
+          <t>2025-02-19 07:00:00-05:00</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr"/>
       <c r="E542" t="inlineStr"/>
       <c r="F542" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>2025-02-19 08:30:00-05:00</t>
+          <t>2025-02-19 07:00:00-05:00</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13451,75 +13459,55 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>2025-02-19 08:30:00-05:00</t>
+          <t>2025-02-19 07:00:00-05:00</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
-      <c r="D544" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
-      <c r="E544" t="inlineStr">
-        <is>
-          <t>1.47M</t>
-        </is>
-      </c>
+      <c r="D544" t="inlineStr"/>
+      <c r="E544" t="inlineStr"/>
       <c r="F544" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>2025-02-19 08:30:00-05:00</t>
+          <t>2025-02-19 07:00:00-05:00</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C545" t="inlineStr"/>
-      <c r="D545" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
-      <c r="E545" t="inlineStr">
-        <is>
-          <t>1.35M</t>
-        </is>
-      </c>
+      <c r="D545" t="inlineStr"/>
+      <c r="E545" t="inlineStr"/>
       <c r="F545" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>2025-02-19 08:30:00-05:00</t>
+          <t>2025-02-19 07:00:00-05:00</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
       <c r="D546" t="inlineStr"/>
-      <c r="E546" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
+      <c r="E546" t="inlineStr"/>
       <c r="F546" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="547">
@@ -13530,7 +13518,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C547" t="inlineStr"/>
@@ -13548,7 +13536,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
@@ -13561,124 +13549,148 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>2025-02-19 08:55:00-05:00</t>
+          <t>2025-02-19 08:30:00-05:00</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Redbook YoYFEB/15</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
       <c r="D549" t="inlineStr"/>
-      <c r="E549" t="inlineStr"/>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
       <c r="F549" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>2025-02-19 08:55:00-05:00</t>
+          <t>2025-02-19 08:30:00-05:00</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Redbook YoYFEB/15</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
       <c r="D550" t="inlineStr"/>
       <c r="E550" t="inlineStr"/>
       <c r="F550" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>2025-02-19 10:30:00-05:00</t>
+          <t>2025-02-19 08:30:00-05:00</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 22.5 to 30 yrs</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
       <c r="D551" t="inlineStr">
         <is>
-          <t>$50 million</t>
-        </is>
-      </c>
-      <c r="E551" t="inlineStr"/>
+          <t>1.39M</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>1.35M</t>
+        </is>
+      </c>
       <c r="F551" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>2025-02-19 11:30:00-05:00</t>
+          <t>2025-02-19 08:30:00-05:00</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
       <c r="D552" t="inlineStr"/>
-      <c r="E552" t="inlineStr"/>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
       <c r="F552" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>2025-02-19 11:30:00-05:00</t>
+          <t>2025-02-19 08:30:00-05:00</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
       <c r="D553" t="inlineStr"/>
-      <c r="E553" t="inlineStr"/>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>-9.0%</t>
+        </is>
+      </c>
       <c r="F553" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>2025-02-19 13:00:00-05:00</t>
+          <t>2025-02-19 08:30:00-05:00</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>20-Year Bond Auction</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
-      <c r="D554" t="inlineStr"/>
-      <c r="E554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>1.47M</t>
+        </is>
+      </c>
       <c r="F554" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>2025-02-19 13:00:00-05:00</t>
+          <t>2025-02-19 08:55:00-05:00</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>20-Year Bond Auction</t>
+          <t>Redbook YoYFEB/15</t>
         </is>
       </c>
       <c r="C555" t="inlineStr"/>
@@ -13691,102 +13703,110 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>2025-02-19 14:00:00-05:00</t>
+          <t>2025-02-19 08:55:00-05:00</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>FOMC Minutes</t>
+          <t>Redbook YoYFEB/15</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
       <c r="D556" t="inlineStr"/>
       <c r="E556" t="inlineStr"/>
       <c r="F556" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>2025-02-19 14:00:00-05:00</t>
+          <t>2025-02-19 10:30:00-05:00</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>FOMC Minutes</t>
+          <t>NY Fed Treasury Purchases 22.5 to 30 yrs</t>
         </is>
       </c>
       <c r="C557" t="inlineStr"/>
-      <c r="D557" t="inlineStr"/>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E557" t="inlineStr"/>
       <c r="F557" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>2025-02-19 16:30:00-05:00</t>
+          <t>2025-02-19 10:30:00-05:00</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>API Crude Oil Stock ChangeFEB/14</t>
+          <t>NY Fed Treasury Purchases 22.5 to 30 yrs</t>
         </is>
       </c>
       <c r="C558" t="inlineStr"/>
-      <c r="D558" t="inlineStr"/>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E558" t="inlineStr"/>
       <c r="F558" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>2025-02-19 16:30:00-05:00</t>
+          <t>2025-02-19 11:30:00-05:00</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>API Crude Oil Stock ChangeFEB/14</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C559" t="inlineStr"/>
       <c r="D559" t="inlineStr"/>
       <c r="E559" t="inlineStr"/>
       <c r="F559" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>2025-02-19 17:00:00-05:00</t>
+          <t>2025-02-19 11:30:00-05:00</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Fed Jefferson Speech</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C560" t="inlineStr"/>
       <c r="D560" t="inlineStr"/>
       <c r="E560" t="inlineStr"/>
       <c r="F560" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>2025-02-20 08:30:00-05:00</t>
+          <t>2025-02-19 13:00:00-05:00</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>20-Year Bond Auction</t>
         </is>
       </c>
       <c r="C561" t="inlineStr"/>
@@ -13799,12 +13819,12 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>2025-02-20 08:30:00-05:00</t>
+          <t>2025-02-19 13:00:00-05:00</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>20-Year Bond Auction</t>
         </is>
       </c>
       <c r="C562" t="inlineStr"/>
@@ -13817,105 +13837,89 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>2025-02-20 08:30:00-05:00</t>
+          <t>2025-02-19 14:00:00-05:00</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>FOMC Minutes</t>
         </is>
       </c>
       <c r="C563" t="inlineStr"/>
       <c r="D563" t="inlineStr"/>
       <c r="E563" t="inlineStr"/>
       <c r="F563" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>2025-02-20 08:30:00-05:00</t>
+          <t>2025-02-19 14:00:00-05:00</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>FOMC Minutes</t>
         </is>
       </c>
       <c r="C564" t="inlineStr"/>
       <c r="D564" t="inlineStr"/>
       <c r="E564" t="inlineStr"/>
       <c r="F564" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>2025-02-20 08:30:00-05:00</t>
+          <t>2025-02-19 16:30:00-05:00</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>API Crude Oil Stock ChangeFEB/14</t>
         </is>
       </c>
       <c r="C565" t="inlineStr"/>
       <c r="D565" t="inlineStr"/>
-      <c r="E565" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E565" t="inlineStr"/>
       <c r="F565" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>2025-02-20 08:30:00-05:00</t>
+          <t>2025-02-19 16:30:00-05:00</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>API Crude Oil Stock ChangeFEB/14</t>
         </is>
       </c>
       <c r="C566" t="inlineStr"/>
       <c r="D566" t="inlineStr"/>
-      <c r="E566" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E566" t="inlineStr"/>
       <c r="F566" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>2025-02-20 08:30:00-05:00</t>
+          <t>2025-02-19 17:00:00-05:00</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Fed Jefferson Speech</t>
         </is>
       </c>
       <c r="C567" t="inlineStr"/>
-      <c r="D567" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E567" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D567" t="inlineStr"/>
+      <c r="E567" t="inlineStr"/>
       <c r="F567" t="n">
         <v>2</v>
       </c>
@@ -13923,25 +13927,17 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>2025-02-20 08:30:00-05:00</t>
+          <t>2025-02-19 17:00:00-05:00</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Fed Jefferson Speech</t>
         </is>
       </c>
       <c r="C568" t="inlineStr"/>
-      <c r="D568" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E568" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D568" t="inlineStr"/>
+      <c r="E568" t="inlineStr"/>
       <c r="F568" t="n">
         <v>2</v>
       </c>
@@ -13954,14 +13950,22 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C569" t="inlineStr"/>
-      <c r="D569" t="inlineStr"/>
-      <c r="E569" t="inlineStr"/>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F569" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="570">
@@ -13990,7 +13994,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
@@ -14008,7 +14012,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C572" t="inlineStr"/>
@@ -14044,7 +14048,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
@@ -14062,12 +14066,16 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
       <c r="D575" t="inlineStr"/>
-      <c r="E575" t="inlineStr"/>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F575" t="n">
         <v>3</v>
       </c>
@@ -14080,12 +14088,16 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
       <c r="D576" t="inlineStr"/>
-      <c r="E576" t="inlineStr"/>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F576" t="n">
         <v>3</v>
       </c>
@@ -14098,7 +14110,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
@@ -14116,7 +14128,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
@@ -14129,17 +14141,25 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>2025-02-20 09:35:00-05:00</t>
+          <t>2025-02-20 08:30:00-05:00</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Fed Golsbee Speech</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
-      <c r="D579" t="inlineStr"/>
-      <c r="E579" t="inlineStr"/>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F579" t="n">
         <v>2</v>
       </c>
@@ -14147,17 +14167,25 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>2025-02-20 09:35:00-05:00</t>
+          <t>2025-02-20 08:30:00-05:00</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Fed Golsbee Speech</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C580" t="inlineStr"/>
-      <c r="D580" t="inlineStr"/>
-      <c r="E580" t="inlineStr"/>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F580" t="n">
         <v>2</v>
       </c>
@@ -14165,12 +14193,12 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>2025-02-20 10:00:00-05:00</t>
+          <t>2025-02-20 08:30:00-05:00</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>CB Leading Index MoMJAN</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C581" t="inlineStr"/>
@@ -14183,25 +14211,17 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>2025-02-20 10:00:00-05:00</t>
+          <t>2025-02-20 08:30:00-05:00</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>CB Leading Index MoMJAN</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
-      <c r="D582" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E582" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+      <c r="D582" t="inlineStr"/>
+      <c r="E582" t="inlineStr"/>
       <c r="F582" t="n">
         <v>3</v>
       </c>
@@ -14209,12 +14229,12 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>2025-02-20 10:30:00-05:00</t>
+          <t>2025-02-20 08:30:00-05:00</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/14</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
@@ -14227,12 +14247,12 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>2025-02-20 10:30:00-05:00</t>
+          <t>2025-02-20 08:30:00-05:00</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/14</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
@@ -14245,12 +14265,12 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>2025-02-20 11:30:00-05:00</t>
+          <t>2025-02-20 08:30:00-05:00</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C585" t="inlineStr"/>
@@ -14263,12 +14283,12 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>2025-02-20 11:30:00-05:00</t>
+          <t>2025-02-20 08:30:00-05:00</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C586" t="inlineStr"/>
@@ -14281,53 +14301,61 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>2025-02-20 11:30:00-05:00</t>
+          <t>2025-02-20 09:35:00-05:00</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>Fed Golsbee Speech</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
       <c r="D587" t="inlineStr"/>
       <c r="E587" t="inlineStr"/>
       <c r="F587" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>2025-02-20 11:30:00-05:00</t>
+          <t>2025-02-20 09:35:00-05:00</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>Fed Golsbee Speech</t>
         </is>
       </c>
       <c r="C588" t="inlineStr"/>
       <c r="D588" t="inlineStr"/>
       <c r="E588" t="inlineStr"/>
       <c r="F588" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>2025-02-20 12:00:00-05:00</t>
+          <t>2025-02-20 10:00:00-05:00</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>CB Leading Index MoMJAN</t>
         </is>
       </c>
       <c r="C589" t="inlineStr"/>
-      <c r="D589" t="inlineStr"/>
-      <c r="E589" t="inlineStr"/>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="F589" t="n">
         <v>3</v>
       </c>
@@ -14335,17 +14363,25 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>2025-02-20 12:00:00-05:00</t>
+          <t>2025-02-20 10:00:00-05:00</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>CB Leading Index MoMJAN</t>
         </is>
       </c>
       <c r="C590" t="inlineStr"/>
-      <c r="D590" t="inlineStr"/>
-      <c r="E590" t="inlineStr"/>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="F590" t="n">
         <v>3</v>
       </c>
@@ -14353,12 +14389,12 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>2025-02-20 12:00:00-05:00</t>
+          <t>2025-02-20 10:30:00-05:00</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C591" t="inlineStr"/>
@@ -14371,12 +14407,12 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>2025-02-20 12:00:00-05:00</t>
+          <t>2025-02-20 10:30:00-05:00</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C592" t="inlineStr"/>
@@ -14389,12 +14425,12 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>2025-02-20 12:00:00-05:00</t>
+          <t>2025-02-20 11:30:00-05:00</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C593" t="inlineStr"/>
@@ -14407,12 +14443,12 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>2025-02-20 12:00:00-05:00</t>
+          <t>2025-02-20 11:30:00-05:00</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
@@ -14425,12 +14461,12 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>2025-02-20 12:00:00-05:00</t>
+          <t>2025-02-20 11:30:00-05:00</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
@@ -14443,12 +14479,12 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>2025-02-20 12:00:00-05:00</t>
+          <t>2025-02-20 11:30:00-05:00</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
@@ -14466,14 +14502,14 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr"/>
       <c r="E597" t="inlineStr"/>
       <c r="F597" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="598">
@@ -14484,7 +14520,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
@@ -14502,14 +14538,14 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr"/>
       <c r="E599" t="inlineStr"/>
       <c r="F599" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="600">
@@ -14520,14 +14556,14 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr"/>
       <c r="F600" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="601">
@@ -14538,7 +14574,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
@@ -14556,7 +14592,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
@@ -14574,14 +14610,14 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr"/>
       <c r="E603" t="inlineStr"/>
       <c r="F603" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="604">
@@ -14592,14 +14628,14 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr"/>
       <c r="E604" t="inlineStr"/>
       <c r="F604" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="605">
@@ -14610,14 +14646,14 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr"/>
       <c r="E605" t="inlineStr"/>
       <c r="F605" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="606">
@@ -14646,7 +14682,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
@@ -14664,7 +14700,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14682,14 +14718,14 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
       <c r="D609" t="inlineStr"/>
       <c r="E609" t="inlineStr"/>
       <c r="F609" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="610">
@@ -14700,14 +14736,14 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
       <c r="D610" t="inlineStr"/>
       <c r="E610" t="inlineStr"/>
       <c r="F610" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="611">
@@ -14731,30 +14767,30 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>2025-02-20 12:05:00-05:00</t>
+          <t>2025-02-20 12:00:00-05:00</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
       <c r="D612" t="inlineStr"/>
       <c r="E612" t="inlineStr"/>
       <c r="F612" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>2025-02-20 13:00:00-05:00</t>
+          <t>2025-02-20 12:00:00-05:00</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>30-Year TIPS Auction</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
@@ -14767,12 +14803,12 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>2025-02-20 13:00:00-05:00</t>
+          <t>2025-02-20 12:00:00-05:00</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>30-Year TIPS Auction</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
@@ -14785,30 +14821,30 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>2025-02-20 14:30:00-05:00</t>
+          <t>2025-02-20 12:00:00-05:00</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
       <c r="D615" t="inlineStr"/>
       <c r="E615" t="inlineStr"/>
       <c r="F615" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>2025-02-20 16:30:00-05:00</t>
+          <t>2025-02-20 12:00:00-05:00</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Fed Balance SheetFEB/19</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -14821,12 +14857,12 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>2025-02-20 16:30:00-05:00</t>
+          <t>2025-02-20 12:00:00-05:00</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Fed Balance SheetFEB/19</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
@@ -14839,61 +14875,53 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>2025-02-20 17:00:00-05:00</t>
+          <t>2025-02-20 12:00:00-05:00</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
       <c r="D618" t="inlineStr"/>
       <c r="E618" t="inlineStr"/>
       <c r="F618" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>2025-02-21 09:45:00-05:00</t>
+          <t>2025-02-20 12:00:00-05:00</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
       <c r="D619" t="inlineStr"/>
-      <c r="E619" t="inlineStr">
-        <is>
-          <t>52.7</t>
-        </is>
-      </c>
+      <c r="E619" t="inlineStr"/>
       <c r="F619" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>2025-02-21 09:45:00-05:00</t>
+          <t>2025-02-20 12:05:00-05:00</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C620" t="inlineStr"/>
       <c r="D620" t="inlineStr"/>
-      <c r="E620" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
+      <c r="E620" t="inlineStr"/>
       <c r="F620" t="n">
         <v>2</v>
       </c>
@@ -14901,25 +14929,17 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>2025-02-21 09:45:00-05:00</t>
+          <t>2025-02-20 12:05:00-05:00</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C621" t="inlineStr"/>
-      <c r="D621" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
-      <c r="E621" t="inlineStr">
-        <is>
-          <t>52.7</t>
-        </is>
-      </c>
+      <c r="D621" t="inlineStr"/>
+      <c r="E621" t="inlineStr"/>
       <c r="F621" t="n">
         <v>2</v>
       </c>
@@ -14927,25 +14947,17 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>2025-02-21 10:00:00-05:00</t>
+          <t>2025-02-20 13:00:00-05:00</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>30-Year TIPS Auction</t>
         </is>
       </c>
       <c r="C622" t="inlineStr"/>
-      <c r="D622" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E622" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+      <c r="D622" t="inlineStr"/>
+      <c r="E622" t="inlineStr"/>
       <c r="F622" t="n">
         <v>3</v>
       </c>
@@ -14953,25 +14965,17 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>2025-02-21 10:00:00-05:00</t>
+          <t>2025-02-20 13:00:00-05:00</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>30-Year TIPS Auction</t>
         </is>
       </c>
       <c r="C623" t="inlineStr"/>
-      <c r="D623" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
-      <c r="E623" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
+      <c r="D623" t="inlineStr"/>
+      <c r="E623" t="inlineStr"/>
       <c r="F623" t="n">
         <v>3</v>
       </c>
@@ -14979,125 +14983,89 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>2025-02-21 10:00:00-05:00</t>
+          <t>2025-02-20 14:30:00-05:00</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C624" t="inlineStr"/>
-      <c r="D624" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
-      <c r="E624" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
+      <c r="D624" t="inlineStr"/>
+      <c r="E624" t="inlineStr"/>
       <c r="F624" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>2025-02-21 10:00:00-05:00</t>
+          <t>2025-02-20 14:30:00-05:00</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C625" t="inlineStr"/>
-      <c r="D625" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E625" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D625" t="inlineStr"/>
+      <c r="E625" t="inlineStr"/>
       <c r="F625" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>2025-02-21 10:00:00-05:00</t>
+          <t>2025-02-20 16:30:00-05:00</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Fed Balance SheetFEB/19</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
-      <c r="D626" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="E626" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
+      <c r="D626" t="inlineStr"/>
+      <c r="E626" t="inlineStr"/>
       <c r="F626" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>2025-02-21 10:00:00-05:00</t>
+          <t>2025-02-20 16:30:00-05:00</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Fed Balance SheetFEB/19</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
-      <c r="D627" t="inlineStr">
-        <is>
-          <t>4.17M</t>
-        </is>
-      </c>
-      <c r="E627" t="inlineStr">
-        <is>
-          <t>4.16M</t>
-        </is>
-      </c>
+      <c r="D627" t="inlineStr"/>
+      <c r="E627" t="inlineStr"/>
       <c r="F627" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>2025-02-21 10:00:00-05:00</t>
+          <t>2025-02-20 17:00:00-05:00</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
       <c r="D628" t="inlineStr"/>
-      <c r="E628" t="inlineStr">
-        <is>
-          <t>-1.7%</t>
-        </is>
-      </c>
+      <c r="E628" t="inlineStr"/>
       <c r="F628" t="n">
         <v>2</v>
       </c>
@@ -15105,12 +15073,12 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>2025-02-21 11:30:00-05:00</t>
+          <t>2025-02-20 17:00:00-05:00</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Fed Jefferson Speech</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C629" t="inlineStr"/>
@@ -15123,53 +15091,69 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>2025-02-21 13:00:00-05:00</t>
+          <t>2025-02-21 09:45:00-05:00</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
-      <c r="D630" t="inlineStr"/>
-      <c r="E630" t="inlineStr"/>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
       <c r="F630" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>2025-02-21 13:00:00-05:00</t>
+          <t>2025-02-21 09:45:00-05:00</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
       <c r="D631" t="inlineStr"/>
-      <c r="E631" t="inlineStr"/>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
       <c r="F631" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>2025-02-24 08:30:00-05:00</t>
+          <t>2025-02-21 09:45:00-05:00</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>Chicago Fed National Activity IndexJAN</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
       <c r="D632" t="inlineStr"/>
-      <c r="E632" t="inlineStr"/>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="F632" t="n">
         <v>2</v>
       </c>
@@ -15177,17 +15161,21 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>2025-02-24 10:30:00-05:00</t>
+          <t>2025-02-21 09:45:00-05:00</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Dallas Fed Manufacturing IndexFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
       <c r="D633" t="inlineStr"/>
-      <c r="E633" t="inlineStr"/>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
       <c r="F633" t="n">
         <v>2</v>
       </c>
@@ -15195,53 +15183,73 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>2025-02-24 11:30:00-05:00</t>
+          <t>2025-02-21 09:45:00-05:00</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr"/>
-      <c r="E634" t="inlineStr"/>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="F634" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>2025-02-24 11:30:00-05:00</t>
+          <t>2025-02-21 09:45:00-05:00</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
-      <c r="D635" t="inlineStr"/>
-      <c r="E635" t="inlineStr"/>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
       <c r="F635" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>2025-02-24 13:00:00-05:00</t>
+          <t>2025-02-21 10:00:00-05:00</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>2-Year Note Auction</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
-      <c r="D636" t="inlineStr"/>
-      <c r="E636" t="inlineStr"/>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="F636" t="n">
         <v>3</v>
       </c>
@@ -15249,17 +15257,25 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>2025-02-25 08:55:00-05:00</t>
+          <t>2025-02-21 10:00:00-05:00</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Redbook YoYFEB/22</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
-      <c r="D637" t="inlineStr"/>
-      <c r="E637" t="inlineStr"/>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="F637" t="n">
         <v>3</v>
       </c>
@@ -15267,39 +15283,51 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>2025-02-25 09:00:00-05:00</t>
+          <t>2025-02-21 10:00:00-05:00</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C638" t="inlineStr"/>
-      <c r="D638" t="inlineStr"/>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F638" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>2025-02-25 09:00:00-05:00</t>
+          <t>2025-02-21 10:00:00-05:00</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
-      <c r="D639" t="inlineStr"/>
-      <c r="E639" t="inlineStr"/>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="F639" t="n">
         <v>3</v>
       </c>
@@ -15307,17 +15335,25 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>2025-02-25 09:00:00-05:00</t>
+          <t>2025-02-21 10:00:00-05:00</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
-      <c r="D640" t="inlineStr"/>
-      <c r="E640" t="inlineStr"/>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="F640" t="n">
         <v>3</v>
       </c>
@@ -15325,71 +15361,99 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>2025-02-25 09:00:00-05:00</t>
+          <t>2025-02-21 10:00:00-05:00</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
-      <c r="D641" t="inlineStr"/>
-      <c r="E641" t="inlineStr"/>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>67.8</t>
+        </is>
+      </c>
       <c r="F641" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>2025-02-25 09:00:00-05:00</t>
+          <t>2025-02-21 10:00:00-05:00</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
       <c r="D642" t="inlineStr"/>
-      <c r="E642" t="inlineStr"/>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>-1.7%</t>
+        </is>
+      </c>
       <c r="F642" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>2025-02-25 10:00:00-05:00</t>
+          <t>2025-02-21 10:00:00-05:00</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
-      <c r="D643" t="inlineStr"/>
-      <c r="E643" t="inlineStr"/>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="F643" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>2025-02-25 10:00:00-05:00</t>
+          <t>2025-02-21 10:00:00-05:00</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
-      <c r="D644" t="inlineStr"/>
-      <c r="E644" t="inlineStr"/>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="F644" t="n">
         <v>3</v>
       </c>
@@ -15397,17 +15461,25 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>2025-02-25 10:00:00-05:00</t>
+          <t>2025-02-21 10:00:00-05:00</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
-      <c r="D645" t="inlineStr"/>
-      <c r="E645" t="inlineStr"/>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
       <c r="F645" t="n">
         <v>3</v>
       </c>
@@ -15415,102 +15487,130 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>2025-02-25 10:00:00-05:00</t>
+          <t>2025-02-21 10:00:00-05:00</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
-      <c r="D646" t="inlineStr"/>
-      <c r="E646" t="inlineStr"/>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>67.8</t>
+        </is>
+      </c>
       <c r="F646" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>2025-02-25 10:30:00-05:00</t>
+          <t>2025-02-21 10:00:00-05:00</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
-      <c r="D647" t="inlineStr"/>
-      <c r="E647" t="inlineStr"/>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>4.16M</t>
+        </is>
+      </c>
       <c r="F647" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>2025-02-25 10:30:00-05:00</t>
+          <t>2025-02-21 10:00:00-05:00</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
-      <c r="D648" t="inlineStr"/>
-      <c r="E648" t="inlineStr"/>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>4.16M</t>
+        </is>
+      </c>
       <c r="F648" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>2025-02-25 13:00:00-05:00</t>
+          <t>2025-02-21 10:00:00-05:00</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr"/>
-      <c r="E649" t="inlineStr"/>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>-1.7%</t>
+        </is>
+      </c>
       <c r="F649" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>2025-02-25 13:00:00-05:00</t>
+          <t>2025-02-21 11:30:00-05:00</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>Fed Jefferson Speech</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
       <c r="D650" t="inlineStr"/>
       <c r="E650" t="inlineStr"/>
       <c r="F650" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>2025-02-25 16:30:00-05:00</t>
+          <t>2025-02-21 11:30:00-05:00</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>API Crude Oil Stock ChangeFEB/21</t>
+          <t>Fed Jefferson Speech</t>
         </is>
       </c>
       <c r="C651" t="inlineStr"/>
@@ -15520,6 +15620,806 @@
         <v>2</v>
       </c>
     </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2025-02-21 13:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr"/>
+      <c r="D652" t="inlineStr"/>
+      <c r="E652" t="inlineStr"/>
+      <c r="F652" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2025-02-21 13:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr"/>
+      <c r="D653" t="inlineStr"/>
+      <c r="E653" t="inlineStr"/>
+      <c r="F653" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2025-02-21 13:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr"/>
+      <c r="D654" t="inlineStr"/>
+      <c r="E654" t="inlineStr"/>
+      <c r="F654" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2025-02-21 13:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr"/>
+      <c r="D655" t="inlineStr"/>
+      <c r="E655" t="inlineStr"/>
+      <c r="F655" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2025-02-24 08:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Chicago Fed National Activity IndexJAN</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr"/>
+      <c r="D656" t="inlineStr"/>
+      <c r="E656" t="inlineStr"/>
+      <c r="F656" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2025-02-24 08:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Chicago Fed National Activity IndexJAN</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr"/>
+      <c r="D657" t="inlineStr"/>
+      <c r="E657" t="inlineStr"/>
+      <c r="F657" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2025-02-24 10:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Dallas Fed Manufacturing IndexFEB</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr"/>
+      <c r="D658" t="inlineStr"/>
+      <c r="E658" t="inlineStr"/>
+      <c r="F658" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2025-02-24 10:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Dallas Fed Manufacturing IndexFEB</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr"/>
+      <c r="D659" t="inlineStr"/>
+      <c r="E659" t="inlineStr"/>
+      <c r="F659" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2025-02-24 11:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>6-Month Bill Auction</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr"/>
+      <c r="D660" t="inlineStr"/>
+      <c r="E660" t="inlineStr"/>
+      <c r="F660" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2025-02-24 11:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>3-Month Bill Auction</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr"/>
+      <c r="D661" t="inlineStr"/>
+      <c r="E661" t="inlineStr"/>
+      <c r="F661" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2025-02-24 11:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>3-Month Bill Auction</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr"/>
+      <c r="D662" t="inlineStr"/>
+      <c r="E662" t="inlineStr"/>
+      <c r="F662" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2025-02-24 11:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>6-Month Bill Auction</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr"/>
+      <c r="D663" t="inlineStr"/>
+      <c r="E663" t="inlineStr"/>
+      <c r="F663" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2025-02-24 13:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>2-Year Note Auction</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr"/>
+      <c r="D664" t="inlineStr"/>
+      <c r="E664" t="inlineStr"/>
+      <c r="F664" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2025-02-24 13:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>2-Year Note Auction</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr"/>
+      <c r="D665" t="inlineStr"/>
+      <c r="E665" t="inlineStr"/>
+      <c r="F665" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2025-02-25 08:55:00-05:00</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Redbook YoYFEB/22</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr"/>
+      <c r="D666" t="inlineStr"/>
+      <c r="E666" t="inlineStr"/>
+      <c r="F666" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2025-02-25 08:55:00-05:00</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Redbook YoYFEB/22</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr"/>
+      <c r="D667" t="inlineStr"/>
+      <c r="E667" t="inlineStr"/>
+      <c r="F667" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2025-02-25 09:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr"/>
+      <c r="D668" t="inlineStr"/>
+      <c r="E668" t="inlineStr"/>
+      <c r="F668" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2025-02-25 09:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>House Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr"/>
+      <c r="D669" t="inlineStr"/>
+      <c r="E669" t="inlineStr"/>
+      <c r="F669" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2025-02-25 09:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>House Price Index MoMDEC</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr"/>
+      <c r="D670" t="inlineStr"/>
+      <c r="E670" t="inlineStr"/>
+      <c r="F670" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2025-02-25 09:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>House Price IndexDEC</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr"/>
+      <c r="D671" t="inlineStr"/>
+      <c r="E671" t="inlineStr"/>
+      <c r="F671" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2025-02-25 09:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr"/>
+      <c r="D672" t="inlineStr"/>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="F672" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2025-02-25 09:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr"/>
+      <c r="D673" t="inlineStr"/>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="F673" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2025-02-25 09:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>House Price IndexDEC</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr"/>
+      <c r="D674" t="inlineStr"/>
+      <c r="E674" t="inlineStr"/>
+      <c r="F674" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2025-02-25 09:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>House Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr"/>
+      <c r="D675" t="inlineStr"/>
+      <c r="E675" t="inlineStr"/>
+      <c r="F675" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2025-02-25 09:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr"/>
+      <c r="D676" t="inlineStr"/>
+      <c r="E676" t="inlineStr"/>
+      <c r="F676" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2025-02-25 09:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>House Price Index MoMDEC</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr"/>
+      <c r="D677" t="inlineStr"/>
+      <c r="E677" t="inlineStr"/>
+      <c r="F677" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2025-02-25 10:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr"/>
+      <c r="D678" t="inlineStr"/>
+      <c r="E678" t="inlineStr"/>
+      <c r="F678" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2025-02-25 10:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>CB Consumer ConfidenceFEB</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr"/>
+      <c r="D679" t="inlineStr"/>
+      <c r="E679" t="inlineStr"/>
+      <c r="F679" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2025-02-25 10:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr"/>
+      <c r="D680" t="inlineStr"/>
+      <c r="E680" t="inlineStr"/>
+      <c r="F680" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2025-02-25 10:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr"/>
+      <c r="D681" t="inlineStr"/>
+      <c r="E681" t="inlineStr"/>
+      <c r="F681" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2025-02-25 10:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr"/>
+      <c r="D682" t="inlineStr"/>
+      <c r="E682" t="inlineStr"/>
+      <c r="F682" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2025-02-25 10:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr"/>
+      <c r="D683" t="inlineStr"/>
+      <c r="E683" t="inlineStr"/>
+      <c r="F683" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2025-02-25 10:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>CB Consumer ConfidenceFEB</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr"/>
+      <c r="D684" t="inlineStr"/>
+      <c r="E684" t="inlineStr"/>
+      <c r="F684" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2025-02-25 10:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr"/>
+      <c r="D685" t="inlineStr"/>
+      <c r="E685" t="inlineStr"/>
+      <c r="F685" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2025-02-25 10:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Dallas Fed Services IndexFEB</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr"/>
+      <c r="D686" t="inlineStr"/>
+      <c r="E686" t="inlineStr"/>
+      <c r="F686" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2025-02-25 10:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr"/>
+      <c r="D687" t="inlineStr"/>
+      <c r="E687" t="inlineStr"/>
+      <c r="F687" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2025-02-25 10:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Dallas Fed Services IndexFEB</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr"/>
+      <c r="D688" t="inlineStr"/>
+      <c r="E688" t="inlineStr"/>
+      <c r="F688" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2025-02-25 10:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr"/>
+      <c r="D689" t="inlineStr"/>
+      <c r="E689" t="inlineStr"/>
+      <c r="F689" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2025-02-25 13:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>5-Year Note Auction</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr"/>
+      <c r="D690" t="inlineStr"/>
+      <c r="E690" t="inlineStr"/>
+      <c r="F690" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2025-02-25 13:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Money SupplyJAN</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr"/>
+      <c r="D691" t="inlineStr"/>
+      <c r="E691" t="inlineStr"/>
+      <c r="F691" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2025-02-25 13:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>5-Year Note Auction</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr"/>
+      <c r="D692" t="inlineStr"/>
+      <c r="E692" t="inlineStr"/>
+      <c r="F692" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2025-02-25 13:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Money SupplyJAN</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr"/>
+      <c r="D693" t="inlineStr"/>
+      <c r="E693" t="inlineStr"/>
+      <c r="F693" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2025-02-25 16:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>API Crude Oil Stock ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr"/>
+      <c r="D694" t="inlineStr"/>
+      <c r="E694" t="inlineStr"/>
+      <c r="F694" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2025-02-25 16:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>API Crude Oil Stock ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr"/>
+      <c r="D695" t="inlineStr"/>
+      <c r="E695" t="inlineStr"/>
+      <c r="F695" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
